--- a/docs/sprint-12-citweb/pbi-7997/evidencias/CT-TDS-008/CT-TDS-008_113241234-EMB-RCV-0000003112027-001_08_2026.xlsx
+++ b/docs/sprint-12-citweb/pbi-7997/evidencias/CT-TDS-008/CT-TDS-008_113241234-EMB-RCV-0000003112027-001_08_2026.xlsx
@@ -524,7 +524,7 @@
               <color rgb="FF000000"/>
               <rFont val="Arial"/>
             </rPr>
-            <t xml:space="preserve">21/08/2026 09:51:15</t>
+            <t xml:space="preserve">21/08/2026 18:27:00</t>
           </r>
         </is>
       </c>
